--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_diff.xlsx
@@ -1,21 +1,205 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\total.carotenes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>LV1_diff</t>
+  </si>
+  <si>
+    <t>LV2_diff</t>
+  </si>
+  <si>
+    <t>LV3_diff</t>
+  </si>
+  <si>
+    <t>LV4_diff</t>
+  </si>
+  <si>
+    <t>LV5_diff</t>
+  </si>
+  <si>
+    <t>LV6_diff</t>
+  </si>
+  <si>
+    <t>LV7_diff</t>
+  </si>
+  <si>
+    <t>LV8_diff</t>
+  </si>
+  <si>
+    <t>LV9_diff</t>
+  </si>
+  <si>
+    <t>LV10_diff</t>
+  </si>
+  <si>
+    <t>LV11_diff</t>
+  </si>
+  <si>
+    <t>LV12_diff</t>
+  </si>
+  <si>
+    <t>LV13_diff</t>
+  </si>
+  <si>
+    <t>LV14_diff</t>
+  </si>
+  <si>
+    <t>LV15_diff</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,13 +245,52 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +332,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +364,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +399,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,2485 +575,2173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_diff</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_diff</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_diff</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_diff</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_diff</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_diff</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_diff</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_diff</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_diff</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_diff</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_diff</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_diff</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_diff</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_diff</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>0.03827044869158608</v>
+        <v>3.5849834047326501E-2</v>
       </c>
       <c r="C2">
-        <v>0.06419243855778234</v>
+        <v>6.1826500660988708E-2</v>
       </c>
       <c r="D2">
-        <v>0.08798722640645851</v>
+        <v>8.6693162946272495E-2</v>
       </c>
       <c r="E2">
-        <v>0.08367410649772733</v>
+        <v>8.396029399678695E-2</v>
       </c>
       <c r="F2">
-        <v>0.1207064703965079</v>
+        <v>0.1244845241506254</v>
       </c>
       <c r="G2">
-        <v>0.1185741873282676</v>
+        <v>0.1187471389188071</v>
       </c>
       <c r="H2">
-        <v>0.1216075017188648</v>
+        <v>0.1198827966656051</v>
       </c>
       <c r="I2">
-        <v>0.1357664947198637</v>
+        <v>0.1317418193124815</v>
       </c>
       <c r="J2">
-        <v>0.1657993417704909</v>
+        <v>0.16583537520105279</v>
       </c>
       <c r="K2">
-        <v>0.1983516919606751</v>
+        <v>0.19790745564708229</v>
       </c>
       <c r="L2">
-        <v>0.2158589832544465</v>
+        <v>0.2185037924581712</v>
       </c>
       <c r="M2">
-        <v>0.2660354930804941</v>
+        <v>0.27175003872199899</v>
       </c>
       <c r="N2">
-        <v>0.3288913608898671</v>
+        <v>0.33066694090821391</v>
       </c>
       <c r="O2">
-        <v>0.3667171540325558</v>
+        <v>0.36352961388356941</v>
       </c>
       <c r="P2">
-        <v>0.3599344418477357</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.35878339017224381</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>0.04191078254707797</v>
+        <v>3.9936795894079953E-2</v>
       </c>
       <c r="C3">
-        <v>0.03907045387414332</v>
+        <v>3.6766182145192561E-2</v>
       </c>
       <c r="D3">
-        <v>0.07454342547148751</v>
+        <v>7.0210342705730011E-2</v>
       </c>
       <c r="E3">
-        <v>0.09633748319188362</v>
+        <v>9.4826224942452297E-2</v>
       </c>
       <c r="F3">
-        <v>0.1451838296460145</v>
+        <v>0.14074606227533959</v>
       </c>
       <c r="G3">
-        <v>0.1818958823478897</v>
+        <v>0.1775086973422545</v>
       </c>
       <c r="H3">
-        <v>0.254948211841117</v>
+        <v>0.24910199973048419</v>
       </c>
       <c r="I3">
-        <v>0.2878959710209066</v>
+        <v>0.28540796046402939</v>
       </c>
       <c r="J3">
-        <v>0.3182794015670669</v>
+        <v>0.31831108275032932</v>
       </c>
       <c r="K3">
-        <v>0.3250473832769651</v>
+        <v>0.331011508595006</v>
       </c>
       <c r="L3">
-        <v>0.3636174030056363</v>
+        <v>0.37287386579671011</v>
       </c>
       <c r="M3">
-        <v>0.4410409339058913</v>
+        <v>0.45273940321922951</v>
       </c>
       <c r="N3">
-        <v>0.5226318129187761</v>
+        <v>0.53733148098375794</v>
       </c>
       <c r="O3">
-        <v>0.5811192844540733</v>
+        <v>0.60060143847510816</v>
       </c>
       <c r="P3">
-        <v>0.6381070024570481</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.65746999230935632</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>0.0335663162943447</v>
+        <v>3.0094334370295961E-2</v>
       </c>
       <c r="C4">
-        <v>0.05442140076357571</v>
+        <v>5.0173536679868902E-2</v>
       </c>
       <c r="D4">
-        <v>0.06900759600808881</v>
+        <v>6.2357528008873619E-2</v>
       </c>
       <c r="E4">
-        <v>0.1097262655687355</v>
+        <v>0.1044748715719683</v>
       </c>
       <c r="F4">
-        <v>0.1325657910493571</v>
+        <v>0.12754336940272459</v>
       </c>
       <c r="G4">
-        <v>0.1320710134158578</v>
+        <v>0.12689938010711771</v>
       </c>
       <c r="H4">
-        <v>0.1277845838048829</v>
+        <v>0.1226308963272614</v>
       </c>
       <c r="I4">
-        <v>0.1625833402381156</v>
+        <v>0.15681066635358221</v>
       </c>
       <c r="J4">
-        <v>0.1989716960450206</v>
+        <v>0.19226575234192361</v>
       </c>
       <c r="K4">
-        <v>0.2947811218930956</v>
+        <v>0.29129197052689387</v>
       </c>
       <c r="L4">
-        <v>0.339452653536728</v>
+        <v>0.33416950887748409</v>
       </c>
       <c r="M4">
-        <v>0.3536391768149121</v>
+        <v>0.34589356425422912</v>
       </c>
       <c r="N4">
-        <v>0.3613394988295945</v>
+        <v>0.35686683350322818</v>
       </c>
       <c r="O4">
-        <v>0.3813704969333306</v>
+        <v>0.37719927953248328</v>
       </c>
       <c r="P4">
-        <v>0.3909084289372861</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.38917632487869508</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>0.02772746043258745</v>
+        <v>2.635473280381595E-2</v>
       </c>
       <c r="C5">
-        <v>0.05538834685495153</v>
+        <v>5.2979890436031678E-2</v>
       </c>
       <c r="D5">
-        <v>0.0887048977796453</v>
+        <v>8.9264292424822589E-2</v>
       </c>
       <c r="E5">
-        <v>0.1219397735679719</v>
+        <v>0.1208581285914772</v>
       </c>
       <c r="F5">
-        <v>0.1729303307192234</v>
+        <v>0.1727448032784574</v>
       </c>
       <c r="G5">
-        <v>0.1851380501525363</v>
+        <v>0.18551682247776999</v>
       </c>
       <c r="H5">
-        <v>0.2069383021122855</v>
+        <v>0.21376665813486101</v>
       </c>
       <c r="I5">
-        <v>0.2445719075533567</v>
+        <v>0.2539334940143827</v>
       </c>
       <c r="J5">
-        <v>0.2986812847390686</v>
+        <v>0.31041312364747647</v>
       </c>
       <c r="K5">
-        <v>0.31747095553954</v>
+        <v>0.33538172621595452</v>
       </c>
       <c r="L5">
-        <v>0.3458774917941933</v>
+        <v>0.36467993103638102</v>
       </c>
       <c r="M5">
-        <v>0.3813903129496284</v>
+        <v>0.40189566611131849</v>
       </c>
       <c r="N5">
-        <v>0.4106809879102958</v>
+        <v>0.43152810539540171</v>
       </c>
       <c r="O5">
-        <v>0.4398517982522857</v>
+        <v>0.45937875346189277</v>
       </c>
       <c r="P5">
-        <v>0.4414759052142175</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.45670478833535122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>0.02714860339019731</v>
+        <v>2.9458350613500221E-2</v>
       </c>
       <c r="C6">
-        <v>0.05382031281657751</v>
+        <v>5.4934703557031783E-2</v>
       </c>
       <c r="D6">
-        <v>0.07684335585576507</v>
+        <v>7.6666909273483852E-2</v>
       </c>
       <c r="E6">
-        <v>0.1273967915800164</v>
+        <v>0.12587551649724471</v>
       </c>
       <c r="F6">
-        <v>0.1513795902958692</v>
+        <v>0.1521955199752206</v>
       </c>
       <c r="G6">
-        <v>0.2083675788290301</v>
+        <v>0.2085860236397559</v>
       </c>
       <c r="H6">
-        <v>0.2147446939328891</v>
+        <v>0.21401866414828349</v>
       </c>
       <c r="I6">
-        <v>0.2617790707717149</v>
+        <v>0.26263773592221978</v>
       </c>
       <c r="J6">
-        <v>0.2842033113257978</v>
+        <v>0.28338670798951149</v>
       </c>
       <c r="K6">
-        <v>0.3080014988235369</v>
+        <v>0.30839634713730468</v>
       </c>
       <c r="L6">
-        <v>0.3521596380216767</v>
+        <v>0.35431191527853001</v>
       </c>
       <c r="M6">
-        <v>0.4154976539174192</v>
+        <v>0.41074366754918218</v>
       </c>
       <c r="N6">
-        <v>0.4704063711815145</v>
+        <v>0.46959957318241202</v>
       </c>
       <c r="O6">
-        <v>0.4879407389994505</v>
+        <v>0.48376176239325852</v>
       </c>
       <c r="P6">
-        <v>0.4661502023269115</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.4602793839587252</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>0.03495633065125719</v>
+        <v>3.066143174289843E-2</v>
       </c>
       <c r="C7">
-        <v>0.05518110395570031</v>
+        <v>4.8022684637931801E-2</v>
       </c>
       <c r="D7">
-        <v>0.08247786234062227</v>
+        <v>7.8626088652325121E-2</v>
       </c>
       <c r="E7">
-        <v>0.07057109475617362</v>
+        <v>6.8688696624634282E-2</v>
       </c>
       <c r="F7">
-        <v>0.08978033288351117</v>
+        <v>8.951407295503333E-2</v>
       </c>
       <c r="G7">
-        <v>0.0820647306630311</v>
+        <v>7.895188010631371E-2</v>
       </c>
       <c r="H7">
-        <v>0.1118049634463095</v>
+        <v>0.11209207761282911</v>
       </c>
       <c r="I7">
-        <v>0.1391679298559848</v>
+        <v>0.13939848092466209</v>
       </c>
       <c r="J7">
-        <v>0.1642797948485519</v>
+        <v>0.1637680051339285</v>
       </c>
       <c r="K7">
-        <v>0.1778848572979504</v>
+        <v>0.17939142325141111</v>
       </c>
       <c r="L7">
-        <v>0.2679422061445784</v>
+        <v>0.26939763066510292</v>
       </c>
       <c r="M7">
-        <v>0.2790906807017332</v>
+        <v>0.28236709074484762</v>
       </c>
       <c r="N7">
-        <v>0.285205140183702</v>
+        <v>0.28662415253019469</v>
       </c>
       <c r="O7">
-        <v>0.2933378193160853</v>
+        <v>0.29627940127272462</v>
       </c>
       <c r="P7">
-        <v>0.3031353653604841</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.30704829833860309</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>0.03052733798233143</v>
+        <v>3.052418206086949E-2</v>
       </c>
       <c r="C8">
-        <v>0.05284769889211072</v>
+        <v>5.0177900076582183E-2</v>
       </c>
       <c r="D8">
-        <v>0.08505909498218867</v>
+        <v>8.1493683091670044E-2</v>
       </c>
       <c r="E8">
-        <v>0.1014572578568615</v>
+        <v>9.9167821770002607E-2</v>
       </c>
       <c r="F8">
-        <v>0.1073231561039183</v>
+        <v>0.10503257144728589</v>
       </c>
       <c r="G8">
-        <v>0.1538544041849046</v>
+        <v>0.1481152904116321</v>
       </c>
       <c r="H8">
-        <v>0.1600220719583283</v>
+        <v>0.15587614155243221</v>
       </c>
       <c r="I8">
-        <v>0.167700805146649</v>
+        <v>0.16352416538302189</v>
       </c>
       <c r="J8">
-        <v>0.2461985461264186</v>
+        <v>0.240149002232072</v>
       </c>
       <c r="K8">
-        <v>0.3047750660603654</v>
+        <v>0.29901716069572798</v>
       </c>
       <c r="L8">
-        <v>0.3288871619931146</v>
+        <v>0.32393749951635248</v>
       </c>
       <c r="M8">
-        <v>0.3279544443872235</v>
+        <v>0.32150484166686433</v>
       </c>
       <c r="N8">
-        <v>0.3205869818720747</v>
+        <v>0.31698797664517347</v>
       </c>
       <c r="O8">
-        <v>0.3549275220678912</v>
+        <v>0.35378220357947288</v>
       </c>
       <c r="P8">
-        <v>0.356870529632636</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.35547206356084432</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>0.02870728465910283</v>
+        <v>2.9335145782027731E-2</v>
       </c>
       <c r="C9">
-        <v>0.05144169140802379</v>
+        <v>5.2453620476225697E-2</v>
       </c>
       <c r="D9">
-        <v>0.08821681771445089</v>
+        <v>8.6867850667210256E-2</v>
       </c>
       <c r="E9">
-        <v>0.1062074701133696</v>
+        <v>0.1029324914321489</v>
       </c>
       <c r="F9">
-        <v>0.1075254596012892</v>
+        <v>0.1062202167795524</v>
       </c>
       <c r="G9">
-        <v>0.1474367555457292</v>
+        <v>0.1463857347483444</v>
       </c>
       <c r="H9">
-        <v>0.1566454751263109</v>
+        <v>0.15251343371473</v>
       </c>
       <c r="I9">
-        <v>0.1551866573861583</v>
+        <v>0.15055999869398271</v>
       </c>
       <c r="J9">
-        <v>0.1999752345321517</v>
+        <v>0.19415537488573881</v>
       </c>
       <c r="K9">
-        <v>0.2479098229394967</v>
+        <v>0.2338283392468532</v>
       </c>
       <c r="L9">
-        <v>0.2824619060945501</v>
+        <v>0.26603906719780013</v>
       </c>
       <c r="M9">
-        <v>0.2747564535134646</v>
+        <v>0.25754887196368759</v>
       </c>
       <c r="N9">
-        <v>0.2597881527726822</v>
+        <v>0.24505954047786641</v>
       </c>
       <c r="O9">
-        <v>0.2850808661053055</v>
+        <v>0.26779794284356839</v>
       </c>
       <c r="P9">
-        <v>0.2988485252336074</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.28700712705934001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>0.0301781214687214</v>
+        <v>2.9214511414555829E-2</v>
       </c>
       <c r="C10">
-        <v>0.05157308978188679</v>
+        <v>5.1593330972031233E-2</v>
       </c>
       <c r="D10">
-        <v>0.08802765203955332</v>
+        <v>8.5405502126499999E-2</v>
       </c>
       <c r="E10">
-        <v>0.1039660535835938</v>
+        <v>0.1033252349813447</v>
       </c>
       <c r="F10">
-        <v>0.1109558911055779</v>
+        <v>0.1098073058847352</v>
       </c>
       <c r="G10">
-        <v>0.1483333156102663</v>
+        <v>0.14838726411321301</v>
       </c>
       <c r="H10">
-        <v>0.1579939299518455</v>
+        <v>0.1584177765741186</v>
       </c>
       <c r="I10">
-        <v>0.154431892864642</v>
+        <v>0.15488995575801651</v>
       </c>
       <c r="J10">
-        <v>0.199764272592813</v>
+        <v>0.19751463195422711</v>
       </c>
       <c r="K10">
-        <v>0.2402034370825125</v>
+        <v>0.23955252520189119</v>
       </c>
       <c r="L10">
-        <v>0.2772501496128253</v>
+        <v>0.27624099141338071</v>
       </c>
       <c r="M10">
-        <v>0.2693674792990123</v>
+        <v>0.26786083673769462</v>
       </c>
       <c r="N10">
-        <v>0.2512206216383082</v>
+        <v>0.2488252872070966</v>
       </c>
       <c r="O10">
-        <v>0.264143386075545</v>
+        <v>0.26301797402354482</v>
       </c>
       <c r="P10">
-        <v>0.2826235018252892</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.27925998547550551</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>0.02942013214522887</v>
+        <v>3.3454430707708198E-2</v>
       </c>
       <c r="C11">
-        <v>0.05268167894493236</v>
+        <v>5.6007485547520219E-2</v>
       </c>
       <c r="D11">
-        <v>0.08663288083779486</v>
+        <v>9.1509495767424398E-2</v>
       </c>
       <c r="E11">
-        <v>0.1044722131862076</v>
+        <v>0.1087257865394959</v>
       </c>
       <c r="F11">
-        <v>0.1076463811287747</v>
+        <v>0.1103641451089252</v>
       </c>
       <c r="G11">
-        <v>0.1518023518785947</v>
+        <v>0.1581010848347445</v>
       </c>
       <c r="H11">
-        <v>0.1583798634698106</v>
+        <v>0.16254759132230509</v>
       </c>
       <c r="I11">
-        <v>0.1535897761092123</v>
+        <v>0.16136525319279721</v>
       </c>
       <c r="J11">
-        <v>0.198831346774163</v>
+        <v>0.20630284021841669</v>
       </c>
       <c r="K11">
-        <v>0.2412676744510979</v>
+        <v>0.2478752100875449</v>
       </c>
       <c r="L11">
-        <v>0.2713269774000702</v>
+        <v>0.28395468619762598</v>
       </c>
       <c r="M11">
-        <v>0.2649750263525958</v>
+        <v>0.27473519047763278</v>
       </c>
       <c r="N11">
-        <v>0.2597734533312297</v>
+        <v>0.26635214802132567</v>
       </c>
       <c r="O11">
-        <v>0.2904461532992604</v>
+        <v>0.29847922845123792</v>
       </c>
       <c r="P11">
-        <v>0.2858290498405294</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.29359710990401278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>0.02606291278420925</v>
+        <v>2.863517952192696E-2</v>
       </c>
       <c r="C12">
-        <v>0.05140446602683768</v>
+        <v>5.6305445891172368E-2</v>
       </c>
       <c r="D12">
-        <v>0.0891644340524218</v>
+        <v>9.344569273683323E-2</v>
       </c>
       <c r="E12">
-        <v>0.1219945884722216</v>
+        <v>0.1247968472062978</v>
       </c>
       <c r="F12">
-        <v>0.1450567678629864</v>
+        <v>0.1469214284183564</v>
       </c>
       <c r="G12">
-        <v>0.1638955611803523</v>
+        <v>0.16756628292318879</v>
       </c>
       <c r="H12">
-        <v>0.1847114087690871</v>
+        <v>0.19019301234406691</v>
       </c>
       <c r="I12">
-        <v>0.2163111206788343</v>
+        <v>0.22232658540085479</v>
       </c>
       <c r="J12">
-        <v>0.2471283497840426</v>
+        <v>0.2583378918935838</v>
       </c>
       <c r="K12">
-        <v>0.2804612874553509</v>
+        <v>0.289216561654565</v>
       </c>
       <c r="L12">
-        <v>0.3261870632642876</v>
+        <v>0.33639675162300359</v>
       </c>
       <c r="M12">
-        <v>0.3735820897341885</v>
+        <v>0.38639662606259118</v>
       </c>
       <c r="N12">
-        <v>0.3948316166692351</v>
+        <v>0.40262673087645101</v>
       </c>
       <c r="O12">
-        <v>0.4205325976277911</v>
+        <v>0.4273705321303834</v>
       </c>
       <c r="P12">
-        <v>0.4446548238418755</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>0.45164221916127922</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
       </c>
       <c r="B13">
-        <v>0.02914504689195829</v>
+        <v>3.0517677915541389E-2</v>
       </c>
       <c r="C13">
-        <v>0.06280509801905698</v>
+        <v>6.6024550863945985E-2</v>
       </c>
       <c r="D13">
-        <v>0.09553555608889319</v>
+        <v>0.1031473592021445</v>
       </c>
       <c r="E13">
-        <v>0.1118155732794034</v>
+        <v>0.1214032455904664</v>
       </c>
       <c r="F13">
-        <v>0.1487579315320617</v>
+        <v>0.1580309129850658</v>
       </c>
       <c r="G13">
-        <v>0.1852445650871833</v>
+        <v>0.19715705209819831</v>
       </c>
       <c r="H13">
-        <v>0.2069969139368593</v>
+        <v>0.21724583056619551</v>
       </c>
       <c r="I13">
-        <v>0.2459860810095481</v>
+        <v>0.25873772583489663</v>
       </c>
       <c r="J13">
-        <v>0.2775999521711758</v>
+        <v>0.29498323538088023</v>
       </c>
       <c r="K13">
-        <v>0.3243936216129045</v>
+        <v>0.34444630755756223</v>
       </c>
       <c r="L13">
-        <v>0.3448634190426059</v>
+        <v>0.36502396216566091</v>
       </c>
       <c r="M13">
-        <v>0.3604656061408527</v>
+        <v>0.3824910356262472</v>
       </c>
       <c r="N13">
-        <v>0.3794972362967591</v>
+        <v>0.40855292484359851</v>
       </c>
       <c r="O13">
-        <v>0.404047737246985</v>
+        <v>0.42892478875107631</v>
       </c>
       <c r="P13">
-        <v>0.4436963286487723</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.46953307360328589</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
       </c>
       <c r="B14">
-        <v>0.03244657536028306</v>
+        <v>2.9490564637684569E-2</v>
       </c>
       <c r="C14">
-        <v>0.05263796996288472</v>
+        <v>4.9903794323547968E-2</v>
       </c>
       <c r="D14">
-        <v>0.08179393275944324</v>
+        <v>7.8511870731845068E-2</v>
       </c>
       <c r="E14">
-        <v>0.06955098279379968</v>
+        <v>6.6656192748985044E-2</v>
       </c>
       <c r="F14">
-        <v>0.08983197359530359</v>
+        <v>8.7628935648084716E-2</v>
       </c>
       <c r="G14">
-        <v>0.08293082726819556</v>
+        <v>8.1985560815950653E-2</v>
       </c>
       <c r="H14">
-        <v>0.1082087303060814</v>
+        <v>0.1061498017299323</v>
       </c>
       <c r="I14">
-        <v>0.1275904134294806</v>
+        <v>0.13002454478531009</v>
       </c>
       <c r="J14">
-        <v>0.1469169083802945</v>
+        <v>0.146815248079563</v>
       </c>
       <c r="K14">
-        <v>0.1529292801359285</v>
+        <v>0.15546648585812001</v>
       </c>
       <c r="L14">
-        <v>0.2312880669043726</v>
+        <v>0.23304007532463081</v>
       </c>
       <c r="M14">
-        <v>0.2590801011174414</v>
+        <v>0.26152138984319939</v>
       </c>
       <c r="N14">
-        <v>0.2669924333321243</v>
+        <v>0.27192992304550678</v>
       </c>
       <c r="O14">
-        <v>0.2680476320155892</v>
+        <v>0.27330595465414842</v>
       </c>
       <c r="P14">
-        <v>0.2568029916012141</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.26569515574182739</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
       </c>
       <c r="B15">
-        <v>0.03414006098876399</v>
+        <v>3.3040124833105589E-2</v>
       </c>
       <c r="C15">
-        <v>0.05491055625980368</v>
+        <v>5.3398126105261963E-2</v>
       </c>
       <c r="D15">
-        <v>0.08208254076657195</v>
+        <v>7.7066259414519056E-2</v>
       </c>
       <c r="E15">
-        <v>0.06845398842894757</v>
+        <v>6.7310050015270351E-2</v>
       </c>
       <c r="F15">
-        <v>0.08926847055242693</v>
+        <v>8.7953593043095135E-2</v>
       </c>
       <c r="G15">
-        <v>0.08293042920800897</v>
+        <v>8.0941281414540822E-2</v>
       </c>
       <c r="H15">
-        <v>0.1074676738627545</v>
+        <v>0.10590226863076101</v>
       </c>
       <c r="I15">
-        <v>0.1275514611323297</v>
+        <v>0.1244788338566695</v>
       </c>
       <c r="J15">
-        <v>0.1461388053443358</v>
+        <v>0.14106846536391529</v>
       </c>
       <c r="K15">
-        <v>0.151697896482515</v>
+        <v>0.1475666683020492</v>
       </c>
       <c r="L15">
-        <v>0.2241662871222655</v>
+        <v>0.21796808523571121</v>
       </c>
       <c r="M15">
-        <v>0.2524259946204199</v>
+        <v>0.24760110695296919</v>
       </c>
       <c r="N15">
-        <v>0.2643450500243179</v>
+        <v>0.25790825347444168</v>
       </c>
       <c r="O15">
-        <v>0.2667840358476827</v>
+        <v>0.25967228425909739</v>
       </c>
       <c r="P15">
-        <v>0.2552036468003116</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>0.24849327717779529</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
       </c>
       <c r="B16">
-        <v>0.03199389748577625</v>
+        <v>2.9315510482610999E-2</v>
       </c>
       <c r="C16">
-        <v>0.05119385415370659</v>
+        <v>4.9243715225747442E-2</v>
       </c>
       <c r="D16">
-        <v>0.07586226761473613</v>
+        <v>7.641541372272409E-2</v>
       </c>
       <c r="E16">
-        <v>0.06704248490590581</v>
+        <v>6.6259415555460555E-2</v>
       </c>
       <c r="F16">
-        <v>0.08659864635824888</v>
+        <v>8.602336672642974E-2</v>
       </c>
       <c r="G16">
-        <v>0.08115849777080708</v>
+        <v>7.9076824970058857E-2</v>
       </c>
       <c r="H16">
-        <v>0.1055959246340318</v>
+        <v>0.1044871767094265</v>
       </c>
       <c r="I16">
-        <v>0.1251649084426707</v>
+        <v>0.1214772659864272</v>
       </c>
       <c r="J16">
-        <v>0.1438130392029037</v>
+        <v>0.14127649565828679</v>
       </c>
       <c r="K16">
-        <v>0.1501949924641161</v>
+        <v>0.14704890565243259</v>
       </c>
       <c r="L16">
-        <v>0.2205604828141249</v>
+        <v>0.21516534455638439</v>
       </c>
       <c r="M16">
-        <v>0.245290469099113</v>
+        <v>0.2397630588452537</v>
       </c>
       <c r="N16">
-        <v>0.2582737254139955</v>
+        <v>0.25372734227901178</v>
       </c>
       <c r="O16">
-        <v>0.2625845080392978</v>
+        <v>0.2563463043386317</v>
       </c>
       <c r="P16">
-        <v>0.2542082024766384</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.24732530311988191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
       </c>
       <c r="B17">
-        <v>0.03068036927097545</v>
+        <v>2.9819822923492719E-2</v>
       </c>
       <c r="C17">
-        <v>0.05153161010948115</v>
+        <v>4.9324575287747703E-2</v>
       </c>
       <c r="D17">
-        <v>0.07975678147667165</v>
+        <v>7.8142224042636266E-2</v>
       </c>
       <c r="E17">
-        <v>0.06990238054389675</v>
+        <v>6.7025740291558278E-2</v>
       </c>
       <c r="F17">
-        <v>0.09107239362910835</v>
+        <v>8.5930519951638695E-2</v>
       </c>
       <c r="G17">
-        <v>0.0826487180783273</v>
+        <v>7.9005302532645594E-2</v>
       </c>
       <c r="H17">
-        <v>0.1077726168942116</v>
+        <v>0.1031883002138194</v>
       </c>
       <c r="I17">
-        <v>0.1263351656910237</v>
+        <v>0.1222918240514371</v>
       </c>
       <c r="J17">
-        <v>0.1462954658163826</v>
+        <v>0.14027005186311861</v>
       </c>
       <c r="K17">
-        <v>0.1512833592567738</v>
+        <v>0.1449743566281797</v>
       </c>
       <c r="L17">
-        <v>0.222961359640783</v>
+        <v>0.21356986726303909</v>
       </c>
       <c r="M17">
-        <v>0.2492525636896309</v>
+        <v>0.2359545106736127</v>
       </c>
       <c r="N17">
-        <v>0.2562761450145888</v>
+        <v>0.24360155730049571</v>
       </c>
       <c r="O17">
-        <v>0.25594126372285</v>
+        <v>0.24324725602464581</v>
       </c>
       <c r="P17">
-        <v>0.2449409516977886</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.23251242939159589</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
       </c>
       <c r="B18">
-        <v>0.02648865549560253</v>
+        <v>2.6508733983242831E-2</v>
       </c>
       <c r="C18">
-        <v>0.05371557583500264</v>
+        <v>5.4464153984057573E-2</v>
       </c>
       <c r="D18">
-        <v>0.09218530022271576</v>
+        <v>9.3500690275286291E-2</v>
       </c>
       <c r="E18">
-        <v>0.1190021594743589</v>
+        <v>0.120948177588845</v>
       </c>
       <c r="F18">
-        <v>0.1448638027208615</v>
+        <v>0.14294746612496639</v>
       </c>
       <c r="G18">
-        <v>0.1820564231843016</v>
+        <v>0.18299106437622811</v>
       </c>
       <c r="H18">
-        <v>0.1838040507208931</v>
+        <v>0.18221033495167249</v>
       </c>
       <c r="I18">
-        <v>0.2158063512996866</v>
+        <v>0.21299442880129829</v>
       </c>
       <c r="J18">
-        <v>0.2307856152524916</v>
+        <v>0.23213721073294891</v>
       </c>
       <c r="K18">
-        <v>0.2530841102858484</v>
+        <v>0.25659112093323022</v>
       </c>
       <c r="L18">
-        <v>0.2730281076560871</v>
+        <v>0.27335057376432048</v>
       </c>
       <c r="M18">
-        <v>0.307531026554691</v>
+        <v>0.30987053447346541</v>
       </c>
       <c r="N18">
-        <v>0.3227325329506845</v>
+        <v>0.32468142817226481</v>
       </c>
       <c r="O18">
-        <v>0.3508871355328684</v>
+        <v>0.35142439929332753</v>
       </c>
       <c r="P18">
-        <v>0.3643327190145477</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.36015706533621722</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
       </c>
       <c r="B19">
-        <v>0.02658740788953096</v>
+        <v>2.523161263443752E-2</v>
       </c>
       <c r="C19">
-        <v>0.05344526301794239</v>
+        <v>5.3588330048016657E-2</v>
       </c>
       <c r="D19">
-        <v>0.07860757472276536</v>
+        <v>7.8975696154559571E-2</v>
       </c>
       <c r="E19">
-        <v>0.1246283987639116</v>
+        <v>0.12401826294065919</v>
       </c>
       <c r="F19">
-        <v>0.139601803400783</v>
+        <v>0.13872212706648299</v>
       </c>
       <c r="G19">
-        <v>0.1629115687143834</v>
+        <v>0.16293225966948169</v>
       </c>
       <c r="H19">
-        <v>0.1734275922708615</v>
+        <v>0.17673054751488659</v>
       </c>
       <c r="I19">
-        <v>0.20283378698354</v>
+        <v>0.21470042669282269</v>
       </c>
       <c r="J19">
-        <v>0.2225950549788752</v>
+        <v>0.23233264203628451</v>
       </c>
       <c r="K19">
-        <v>0.2268153611721341</v>
+        <v>0.23629490258321051</v>
       </c>
       <c r="L19">
-        <v>0.2683785851121553</v>
+        <v>0.28036282561121012</v>
       </c>
       <c r="M19">
-        <v>0.3005214691060282</v>
+        <v>0.3098861969767337</v>
       </c>
       <c r="N19">
-        <v>0.3218745912108466</v>
+        <v>0.32430128549532461</v>
       </c>
       <c r="O19">
-        <v>0.3361492880281889</v>
+        <v>0.3395676006830578</v>
       </c>
       <c r="P19">
-        <v>0.3427707855308545</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.34261592486168319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
       </c>
       <c r="B20">
-        <v>0.02437710242661972</v>
+        <v>2.5151718983279951E-2</v>
       </c>
       <c r="C20">
-        <v>0.04704001133384317</v>
+        <v>4.7963141445958701E-2</v>
       </c>
       <c r="D20">
-        <v>0.08337524401244856</v>
+        <v>8.3885541850163614E-2</v>
       </c>
       <c r="E20">
-        <v>0.1368295894602365</v>
+        <v>0.13716943728388181</v>
       </c>
       <c r="F20">
-        <v>0.1507080722377147</v>
+        <v>0.15248740061478089</v>
       </c>
       <c r="G20">
-        <v>0.1462807162220482</v>
+        <v>0.1463535638751258</v>
       </c>
       <c r="H20">
-        <v>0.1635929138449214</v>
+        <v>0.16512420871784431</v>
       </c>
       <c r="I20">
-        <v>0.1839186612909515</v>
+        <v>0.18782842412438061</v>
       </c>
       <c r="J20">
-        <v>0.1969652155933156</v>
+        <v>0.20157964839609799</v>
       </c>
       <c r="K20">
-        <v>0.2127781097522669</v>
+        <v>0.2170261530347819</v>
       </c>
       <c r="L20">
-        <v>0.245329388536113</v>
+        <v>0.25020975950402141</v>
       </c>
       <c r="M20">
-        <v>0.2887751874380113</v>
+        <v>0.29226281209809191</v>
       </c>
       <c r="N20">
-        <v>0.3134795207907564</v>
+        <v>0.31092946447493558</v>
       </c>
       <c r="O20">
-        <v>0.305486078069355</v>
+        <v>0.29790574730263708</v>
       </c>
       <c r="P20">
-        <v>0.319243949000362</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.31270073496895989</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>0.03920997587907238</v>
+        <v>3.8789347127973613E-2</v>
       </c>
       <c r="C21">
-        <v>0.0374107357374297</v>
+        <v>3.6057367124108231E-2</v>
       </c>
       <c r="D21">
-        <v>0.0689515887775427</v>
+        <v>6.5510223499171905E-2</v>
       </c>
       <c r="E21">
-        <v>0.088955238335506</v>
+        <v>8.4942793259921379E-2</v>
       </c>
       <c r="F21">
-        <v>0.1375289703429698</v>
+        <v>0.1314225757770657</v>
       </c>
       <c r="G21">
-        <v>0.1922071939917004</v>
+        <v>0.18201368391217759</v>
       </c>
       <c r="H21">
-        <v>0.2739220534323862</v>
+        <v>0.2592933006319143</v>
       </c>
       <c r="I21">
-        <v>0.3185341376353839</v>
+        <v>0.30158936500293632</v>
       </c>
       <c r="J21">
-        <v>0.3368819721846676</v>
+        <v>0.33091278837848709</v>
       </c>
       <c r="K21">
-        <v>0.3714383677833595</v>
+        <v>0.36134644250634251</v>
       </c>
       <c r="L21">
-        <v>0.410542196065684</v>
+        <v>0.40303320619603678</v>
       </c>
       <c r="M21">
-        <v>0.4607689464768873</v>
+        <v>0.45274820759134021</v>
       </c>
       <c r="N21">
-        <v>0.5164513714626633</v>
+        <v>0.50734427901557644</v>
       </c>
       <c r="O21">
-        <v>0.5809619420876816</v>
+        <v>0.57100132707926254</v>
       </c>
       <c r="P21">
-        <v>0.6603847599841767</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.64826241266173745</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
       </c>
       <c r="B22">
-        <v>0.04023502906077886</v>
+        <v>3.7900439509180872E-2</v>
       </c>
       <c r="C22">
-        <v>0.03844808103350161</v>
+        <v>3.7285920857435539E-2</v>
       </c>
       <c r="D22">
-        <v>0.0659798620806531</v>
+        <v>6.6848327220168646E-2</v>
       </c>
       <c r="E22">
-        <v>0.08317285028423771</v>
+        <v>8.289323584303443E-2</v>
       </c>
       <c r="F22">
-        <v>0.1325796146929502</v>
+        <v>0.13652604696245449</v>
       </c>
       <c r="G22">
-        <v>0.1630230941869627</v>
+        <v>0.1663888183618468</v>
       </c>
       <c r="H22">
-        <v>0.2602203049784706</v>
+        <v>0.26390457095906172</v>
       </c>
       <c r="I22">
-        <v>0.3195884130833434</v>
+        <v>0.32014291187093241</v>
       </c>
       <c r="J22">
-        <v>0.3274682123803167</v>
+        <v>0.33041185030214931</v>
       </c>
       <c r="K22">
-        <v>0.3620793251062591</v>
+        <v>0.36074534135605502</v>
       </c>
       <c r="L22">
-        <v>0.3994192871487508</v>
+        <v>0.40158536051531668</v>
       </c>
       <c r="M22">
-        <v>0.4530475312406342</v>
+        <v>0.45648690025390642</v>
       </c>
       <c r="N22">
-        <v>0.4992925561561345</v>
+        <v>0.50470072941373867</v>
       </c>
       <c r="O22">
-        <v>0.5596881001784557</v>
+        <v>0.5698045282899501</v>
       </c>
       <c r="P22">
-        <v>0.6237044306662591</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.63681031641674868</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>37</v>
       </c>
       <c r="B23">
-        <v>0.02577103115999235</v>
+        <v>2.605927448699941E-2</v>
       </c>
       <c r="C23">
-        <v>0.06794551209164412</v>
+        <v>7.0889585182583148E-2</v>
       </c>
       <c r="D23">
-        <v>0.09248044397260258</v>
+        <v>9.1532431797047287E-2</v>
       </c>
       <c r="E23">
-        <v>0.08771154580853691</v>
+        <v>8.5061471257432353E-2</v>
       </c>
       <c r="F23">
-        <v>0.1545856893086129</v>
+        <v>0.1509014540557029</v>
       </c>
       <c r="G23">
-        <v>0.2658382764750071</v>
+        <v>0.2604761274932163</v>
       </c>
       <c r="H23">
-        <v>0.3655153749791236</v>
+        <v>0.36079363386415492</v>
       </c>
       <c r="I23">
-        <v>0.3940716516271262</v>
+        <v>0.39059856773948121</v>
       </c>
       <c r="J23">
-        <v>0.4587746500422304</v>
+        <v>0.45086274395338038</v>
       </c>
       <c r="K23">
-        <v>0.5187818446351593</v>
+        <v>0.51207288805120998</v>
       </c>
       <c r="L23">
-        <v>0.5910530477679251</v>
+        <v>0.58526233008673456</v>
       </c>
       <c r="M23">
-        <v>0.6265389628593554</v>
+        <v>0.62136895948416782</v>
       </c>
       <c r="N23">
-        <v>0.689020232154703</v>
+        <v>0.68404831829863422</v>
       </c>
       <c r="O23">
-        <v>0.743551339528993</v>
+        <v>0.74152141236548486</v>
       </c>
       <c r="P23">
-        <v>0.8123465613694384</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.8141381184787968</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>38</v>
       </c>
       <c r="B24">
-        <v>0.06394942841126716</v>
+        <v>2.243736699124654E-2</v>
       </c>
       <c r="C24">
-        <v>0.1748381651125587</v>
+        <v>4.0881458646397813E-2</v>
       </c>
       <c r="D24">
-        <v>0.1736118860396061</v>
+        <v>5.5970763712909648E-2</v>
       </c>
       <c r="E24">
-        <v>0.2863100527348237</v>
+        <v>5.8903517654139592E-2</v>
       </c>
       <c r="F24">
-        <v>0.7345700791509959</v>
+        <v>8.9471235758721734E-2</v>
       </c>
       <c r="G24">
-        <v>0.6828746351556498</v>
+        <v>0.1002747006202156</v>
       </c>
       <c r="H24">
-        <v>0.7914252505034298</v>
+        <v>0.1152213682395464</v>
       </c>
       <c r="I24">
-        <v>0.8923777603955002</v>
+        <v>0.16566075731131999</v>
       </c>
       <c r="J24">
-        <v>1.03292426395543</v>
+        <v>0.16992832945480049</v>
       </c>
       <c r="K24">
-        <v>1.104055416991785</v>
+        <v>0.18565332900346401</v>
       </c>
       <c r="L24">
-        <v>1.183772076838638</v>
+        <v>0.22690725886090721</v>
       </c>
       <c r="M24">
-        <v>1.23481640352248</v>
+        <v>0.27024697571132161</v>
       </c>
       <c r="N24">
-        <v>1.278613197391012</v>
+        <v>0.31854082750169771</v>
       </c>
       <c r="O24">
-        <v>1.341294409779573</v>
+        <v>0.35269851955108661</v>
       </c>
       <c r="P24">
-        <v>1.376616478937166</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.396321315819814</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>39</v>
       </c>
       <c r="B25">
-        <v>0.08478026457198104</v>
+        <v>2.497147562870938E-2</v>
       </c>
       <c r="C25">
-        <v>0.1775389956869138</v>
+        <v>4.2929248374491302E-2</v>
       </c>
       <c r="D25">
-        <v>0.2438536549218989</v>
+        <v>5.9140508203996973E-2</v>
       </c>
       <c r="E25">
-        <v>0.4071567496836282</v>
+        <v>5.6899216818820819E-2</v>
       </c>
       <c r="F25">
-        <v>0.5506277529468504</v>
+        <v>8.5829920552780381E-2</v>
       </c>
       <c r="G25">
-        <v>0.7298811735758078</v>
+        <v>8.1319720692217157E-2</v>
       </c>
       <c r="H25">
-        <v>0.9457127116760058</v>
+        <v>9.2391457986271686E-2</v>
       </c>
       <c r="I25">
-        <v>1.082403139087747</v>
+        <v>0.15906705806599791</v>
       </c>
       <c r="J25">
-        <v>1.163223986771432</v>
+        <v>0.13528937903961991</v>
       </c>
       <c r="K25">
-        <v>1.223859712961835</v>
+        <v>0.1483019741520801</v>
       </c>
       <c r="L25">
-        <v>1.359003133059216</v>
+        <v>0.1656438798148957</v>
       </c>
       <c r="M25">
-        <v>1.482901701404317</v>
+        <v>0.19643263617247919</v>
       </c>
       <c r="N25">
-        <v>1.582432517329115</v>
+        <v>0.22910291678313091</v>
       </c>
       <c r="O25">
-        <v>1.641674014416103</v>
+        <v>0.25903756846150472</v>
       </c>
       <c r="P25">
-        <v>1.689169345985587</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.29555357240832358</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
       </c>
       <c r="B26">
-        <v>0.06333590543308676</v>
+        <v>2.1684241224405709E-2</v>
       </c>
       <c r="C26">
-        <v>0.1274940903447309</v>
+        <v>4.0393825290136347E-2</v>
       </c>
       <c r="D26">
-        <v>0.1394669073512667</v>
+        <v>7.3892470304586344E-2</v>
       </c>
       <c r="E26">
-        <v>0.2406247248877298</v>
+        <v>6.4822236599828553E-2</v>
       </c>
       <c r="F26">
-        <v>0.4022311697433184</v>
+        <v>9.2734162346890803E-2</v>
       </c>
       <c r="G26">
-        <v>0.4809961695671876</v>
+        <v>8.9483768578062062E-2</v>
       </c>
       <c r="H26">
-        <v>0.6250628774054141</v>
+        <v>9.9509538382491547E-2</v>
       </c>
       <c r="I26">
-        <v>0.6436932291817183</v>
+        <v>0.13114827833238951</v>
       </c>
       <c r="J26">
-        <v>0.5915291593965699</v>
+        <v>0.1696341198143341</v>
       </c>
       <c r="K26">
-        <v>0.5889932798607662</v>
+        <v>0.19193248077082481</v>
       </c>
       <c r="L26">
-        <v>0.772259554292119</v>
+        <v>0.2172293014380875</v>
       </c>
       <c r="M26">
-        <v>0.9645471304508679</v>
+        <v>0.23685357808726951</v>
       </c>
       <c r="N26">
-        <v>0.9499550556417711</v>
+        <v>0.27212506132112368</v>
       </c>
       <c r="O26">
-        <v>1.018706201081703</v>
+        <v>0.30986514331128823</v>
       </c>
       <c r="P26">
-        <v>1.04548358722351</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.34730866742723598</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
       </c>
       <c r="B27">
-        <v>0.06856557555185389</v>
+        <v>2.105287081467011E-2</v>
       </c>
       <c r="C27">
-        <v>0.116227022284798</v>
+        <v>4.0698941384524012E-2</v>
       </c>
       <c r="D27">
-        <v>0.3053375667528497</v>
+        <v>7.2263805265656345E-2</v>
       </c>
       <c r="E27">
-        <v>0.270967982365341</v>
+        <v>6.4518130486507563E-2</v>
       </c>
       <c r="F27">
-        <v>0.4737397666658635</v>
+        <v>9.0201596354432478E-2</v>
       </c>
       <c r="G27">
-        <v>0.5292604128060515</v>
+        <v>8.2847814070385328E-2</v>
       </c>
       <c r="H27">
-        <v>0.5042495192006531</v>
+        <v>9.2793319632209492E-2</v>
       </c>
       <c r="I27">
-        <v>0.5488985368022858</v>
+        <v>0.1111625804346716</v>
       </c>
       <c r="J27">
-        <v>0.7049865929075604</v>
+        <v>0.14061461501478151</v>
       </c>
       <c r="K27">
-        <v>0.8012706788789129</v>
+        <v>0.1581015939148277</v>
       </c>
       <c r="L27">
-        <v>0.8972207197212581</v>
+        <v>0.16791173736937209</v>
       </c>
       <c r="M27">
-        <v>1.028953553952179</v>
+        <v>0.18339685720226789</v>
       </c>
       <c r="N27">
-        <v>0.9773492785907087</v>
+        <v>0.2155374701231747</v>
       </c>
       <c r="O27">
-        <v>1.121924555095369</v>
+        <v>0.25081589910093249</v>
       </c>
       <c r="P27">
-        <v>1.187679320969593</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.2494102694631313</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>42</v>
       </c>
       <c r="B28">
-        <v>0.02231377328530193</v>
+        <v>2.263424989068796E-2</v>
       </c>
       <c r="C28">
-        <v>0.03971100471529709</v>
+        <v>3.8970376334818257E-2</v>
       </c>
       <c r="D28">
-        <v>0.05567609411047314</v>
+        <v>5.5820600963102263E-2</v>
       </c>
       <c r="E28">
-        <v>0.05822822573930075</v>
+        <v>5.4746053360025249E-2</v>
       </c>
       <c r="F28">
-        <v>0.08885392382494484</v>
+        <v>8.2215817598339513E-2</v>
       </c>
       <c r="G28">
-        <v>0.1007533378916394</v>
+        <v>7.7652731888258719E-2</v>
       </c>
       <c r="H28">
-        <v>0.1128684153959364</v>
+        <v>8.5608451541758557E-2</v>
       </c>
       <c r="I28">
-        <v>0.1652703613705555</v>
+        <v>0.14087092794898279</v>
       </c>
       <c r="J28">
-        <v>0.1699541407538165</v>
+        <v>0.1154482965782208</v>
       </c>
       <c r="K28">
-        <v>0.184354319037778</v>
+        <v>0.1131355170404299</v>
       </c>
       <c r="L28">
-        <v>0.2220647312959189</v>
+        <v>0.1166132669644673</v>
       </c>
       <c r="M28">
-        <v>0.2660957234132028</v>
+        <v>0.1341035906319972</v>
       </c>
       <c r="N28">
-        <v>0.3139534933160499</v>
+        <v>0.14950115745677869</v>
       </c>
       <c r="O28">
-        <v>0.3459513947170592</v>
+        <v>0.1711868705061729</v>
       </c>
       <c r="P28">
-        <v>0.3929046090293439</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.2263737942444507</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>43</v>
       </c>
       <c r="B29">
-        <v>0.02121712409333487</v>
+        <v>2.4947144263888891E-2</v>
       </c>
       <c r="C29">
-        <v>0.03835849060861241</v>
+        <v>4.3557040763158583E-2</v>
       </c>
       <c r="D29">
-        <v>0.05609267642729321</v>
+        <v>6.075962781221933E-2</v>
       </c>
       <c r="E29">
-        <v>0.05364019410311593</v>
+        <v>5.8089148984708072E-2</v>
       </c>
       <c r="F29">
-        <v>0.084119983026684</v>
+        <v>8.3974509230463679E-2</v>
       </c>
       <c r="G29">
-        <v>0.07789250344797027</v>
+        <v>7.8221472618508203E-2</v>
       </c>
       <c r="H29">
-        <v>0.0874260973228842</v>
+        <v>8.5147166165508104E-2</v>
       </c>
       <c r="I29">
-        <v>0.1537908883601048</v>
+        <v>0.1410472676188412</v>
       </c>
       <c r="J29">
-        <v>0.1336832020611013</v>
+        <v>0.1158947589684423</v>
       </c>
       <c r="K29">
-        <v>0.1439792766965764</v>
+        <v>0.11211064224097179</v>
       </c>
       <c r="L29">
-        <v>0.1617586530880357</v>
+        <v>0.1144137057411516</v>
       </c>
       <c r="M29">
-        <v>0.1920052468461887</v>
+        <v>0.13251988111774671</v>
       </c>
       <c r="N29">
-        <v>0.2243391584008704</v>
+        <v>0.14900470655345591</v>
       </c>
       <c r="O29">
-        <v>0.2557598168810639</v>
+        <v>0.16682645388525841</v>
       </c>
       <c r="P29">
-        <v>0.2925054921559843</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.22394136286434699</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>44</v>
       </c>
       <c r="B30">
-        <v>0.02211461804056114</v>
+        <v>2.365978067130636E-2</v>
       </c>
       <c r="C30">
-        <v>0.04100054375000084</v>
+        <v>4.1361229569238489E-2</v>
       </c>
       <c r="D30">
-        <v>0.07465255902925849</v>
+        <v>5.7718141089997177E-2</v>
       </c>
       <c r="E30">
-        <v>0.06775543454367527</v>
+        <v>5.6698825353232229E-2</v>
       </c>
       <c r="F30">
-        <v>0.09420189338820761</v>
+        <v>8.1722660206462683E-2</v>
       </c>
       <c r="G30">
-        <v>0.09066977131842358</v>
+        <v>7.9900656151988048E-2</v>
       </c>
       <c r="H30">
-        <v>0.1068640325312135</v>
+        <v>8.418408845085279E-2</v>
       </c>
       <c r="I30">
-        <v>0.1344593996208975</v>
+        <v>0.13941188227864271</v>
       </c>
       <c r="J30">
-        <v>0.1745924133100396</v>
+        <v>0.1147917810502431</v>
       </c>
       <c r="K30">
-        <v>0.1980972287694479</v>
+        <v>0.113381398034836</v>
       </c>
       <c r="L30">
-        <v>0.2207700540834392</v>
+        <v>0.112798098827243</v>
       </c>
       <c r="M30">
-        <v>0.2426590661038752</v>
+        <v>0.1286309028090219</v>
       </c>
       <c r="N30">
-        <v>0.2777873674350306</v>
+        <v>0.14346058507031231</v>
       </c>
       <c r="O30">
-        <v>0.3147678301002813</v>
+        <v>0.16393871848996319</v>
       </c>
       <c r="P30">
-        <v>0.3521622717896061</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.21666618252379691</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>45</v>
       </c>
       <c r="B31">
-        <v>0.01924674135292148</v>
+        <v>2.4441612894340881E-2</v>
       </c>
       <c r="C31">
-        <v>0.03808918600123357</v>
+        <v>4.1486565258832098E-2</v>
       </c>
       <c r="D31">
-        <v>0.07095382167796715</v>
+        <v>5.8003202630420032E-2</v>
       </c>
       <c r="E31">
-        <v>0.06197087757389541</v>
+        <v>5.6259220126815057E-2</v>
       </c>
       <c r="F31">
-        <v>0.08779535013451789</v>
+        <v>8.5351768157435948E-2</v>
       </c>
       <c r="G31">
-        <v>0.08189708241370308</v>
+        <v>8.1425802535431302E-2</v>
       </c>
       <c r="H31">
-        <v>0.0920691822654961</v>
+        <v>8.6924820662366176E-2</v>
       </c>
       <c r="I31">
-        <v>0.1109521166309262</v>
+        <v>0.1476793343482545</v>
       </c>
       <c r="J31">
-        <v>0.1381172290579474</v>
+        <v>0.11912756399133451</v>
       </c>
       <c r="K31">
-        <v>0.1546163137905233</v>
+        <v>0.1133196384949228</v>
       </c>
       <c r="L31">
-        <v>0.1637917272259651</v>
+        <v>0.1118719636093173</v>
       </c>
       <c r="M31">
-        <v>0.1783890795943055</v>
+        <v>0.12912144158786629</v>
       </c>
       <c r="N31">
-        <v>0.2084471053069301</v>
+        <v>0.14428288027392319</v>
       </c>
       <c r="O31">
-        <v>0.2469433598023775</v>
+        <v>0.15717784426879111</v>
       </c>
       <c r="P31">
-        <v>0.2449750977760358</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.20817666256045919</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>46</v>
       </c>
       <c r="B32">
-        <v>0.02216330238158104</v>
+        <v>2.2886340019660171E-2</v>
       </c>
       <c r="C32">
-        <v>0.03880700846391927</v>
+        <v>4.0493761229749459E-2</v>
       </c>
       <c r="D32">
-        <v>0.05707901740166788</v>
+        <v>5.7677413839969049E-2</v>
       </c>
       <c r="E32">
-        <v>0.05573123043165751</v>
+        <v>5.51451965728319E-2</v>
       </c>
       <c r="F32">
-        <v>0.08290439793537063</v>
+        <v>8.4156745718796166E-2</v>
       </c>
       <c r="G32">
-        <v>0.07852889423601594</v>
+        <v>7.7810664242719429E-2</v>
       </c>
       <c r="H32">
-        <v>0.08303523371350963</v>
+        <v>8.6949006622728309E-2</v>
       </c>
       <c r="I32">
-        <v>0.1380012861144801</v>
+        <v>0.14143661283127121</v>
       </c>
       <c r="J32">
-        <v>0.1166582004070874</v>
+        <v>0.1173933499224329</v>
       </c>
       <c r="K32">
-        <v>0.1110335284001207</v>
+        <v>0.1182273595338158</v>
       </c>
       <c r="L32">
-        <v>0.1138818034026238</v>
+        <v>0.1280642302044103</v>
       </c>
       <c r="M32">
-        <v>0.1303175480899008</v>
+        <v>0.14811487382583691</v>
       </c>
       <c r="N32">
-        <v>0.1457859574748775</v>
+        <v>0.16452963712517391</v>
       </c>
       <c r="O32">
-        <v>0.1656307343359102</v>
+        <v>0.18706874474737989</v>
       </c>
       <c r="P32">
-        <v>0.2186017551443684</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.23104749654607659</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>47</v>
       </c>
       <c r="B33">
-        <v>0.02434742101054888</v>
+        <v>2.251594750639507E-2</v>
       </c>
       <c r="C33">
-        <v>0.04168884493335412</v>
+        <v>4.0356748885906457E-2</v>
       </c>
       <c r="D33">
-        <v>0.05747012975491606</v>
+        <v>5.8377938216666148E-2</v>
       </c>
       <c r="E33">
-        <v>0.05603839005164002</v>
+        <v>5.5239868198408093E-2</v>
       </c>
       <c r="F33">
-        <v>0.08062535786765146</v>
+        <v>8.4007093535522048E-2</v>
       </c>
       <c r="G33">
-        <v>0.07618802372032696</v>
+        <v>7.7819988361794601E-2</v>
       </c>
       <c r="H33">
-        <v>0.08071128532180305</v>
+        <v>8.6270804665864453E-2</v>
       </c>
       <c r="I33">
-        <v>0.1357767119633035</v>
+        <v>0.13834314808692791</v>
       </c>
       <c r="J33">
-        <v>0.1131061220462801</v>
+        <v>0.11655366704064229</v>
       </c>
       <c r="K33">
-        <v>0.1082896430601585</v>
+        <v>0.11565926589007471</v>
       </c>
       <c r="L33">
-        <v>0.1128355534472887</v>
+        <v>0.1245785958992274</v>
       </c>
       <c r="M33">
-        <v>0.1297427696451124</v>
+        <v>0.1423019081557956</v>
       </c>
       <c r="N33">
-        <v>0.1434073933445633</v>
+        <v>0.1602361645238376</v>
       </c>
       <c r="O33">
-        <v>0.1660836010714892</v>
+        <v>0.18176809274816691</v>
       </c>
       <c r="P33">
-        <v>0.2223921685902331</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.2299405167722943</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>48</v>
       </c>
       <c r="B34">
-        <v>0.02253342433672101</v>
+        <v>2.2286884800004399E-2</v>
       </c>
       <c r="C34">
-        <v>0.03953966304939516</v>
+        <v>3.916405351370289E-2</v>
       </c>
       <c r="D34">
-        <v>0.05649074962940981</v>
+        <v>5.6555371104001113E-2</v>
       </c>
       <c r="E34">
-        <v>0.05476252452473773</v>
+        <v>5.4782179521331131E-2</v>
       </c>
       <c r="F34">
-        <v>0.08155794636071889</v>
+        <v>8.2799912125035013E-2</v>
       </c>
       <c r="G34">
-        <v>0.0774998561516218</v>
+        <v>7.5580046870613815E-2</v>
       </c>
       <c r="H34">
-        <v>0.08186867565550759</v>
+        <v>8.3309548592129135E-2</v>
       </c>
       <c r="I34">
-        <v>0.1426830175641429</v>
+        <v>0.13440052017064941</v>
       </c>
       <c r="J34">
-        <v>0.1166419103277806</v>
+        <v>0.114833146279589</v>
       </c>
       <c r="K34">
-        <v>0.1110260226216244</v>
+        <v>0.11251728078010741</v>
       </c>
       <c r="L34">
-        <v>0.1116534587048851</v>
+        <v>0.12118976100768659</v>
       </c>
       <c r="M34">
-        <v>0.128631251810443</v>
+        <v>0.13879385020580881</v>
       </c>
       <c r="N34">
-        <v>0.1418265555320044</v>
+        <v>0.1560866527183187</v>
       </c>
       <c r="O34">
-        <v>0.1589543207710605</v>
+        <v>0.17763024135638911</v>
       </c>
       <c r="P34">
-        <v>0.2107558912312376</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>0.22746690034801759</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>49</v>
       </c>
       <c r="B35">
-        <v>0.02406684987299346</v>
+        <v>2.4798366077067872E-2</v>
       </c>
       <c r="C35">
-        <v>0.04090162245113471</v>
+        <v>4.1889184030514108E-2</v>
       </c>
       <c r="D35">
-        <v>0.05751869890315531</v>
+        <v>5.7726031711046948E-2</v>
       </c>
       <c r="E35">
-        <v>0.05457085808508122</v>
+        <v>5.5627087556803227E-2</v>
       </c>
       <c r="F35">
-        <v>0.07979685723786489</v>
+        <v>8.3759744330525576E-2</v>
       </c>
       <c r="G35">
-        <v>0.07633595532364523</v>
+        <v>8.0464942908417325E-2</v>
       </c>
       <c r="H35">
-        <v>0.08141569619145905</v>
+        <v>8.6042935899755757E-2</v>
       </c>
       <c r="I35">
-        <v>0.1408406231151781</v>
+        <v>0.13866154383308621</v>
       </c>
       <c r="J35">
-        <v>0.1177114803359685</v>
+        <v>0.1151266467061004</v>
       </c>
       <c r="K35">
-        <v>0.1109491958508729</v>
+        <v>0.11501935777671531</v>
       </c>
       <c r="L35">
-        <v>0.1073608213827332</v>
+        <v>0.11975511530976871</v>
       </c>
       <c r="M35">
-        <v>0.1249223194619845</v>
+        <v>0.13824207752236289</v>
       </c>
       <c r="N35">
-        <v>0.1377943161553913</v>
+        <v>0.15115930928470159</v>
       </c>
       <c r="O35">
-        <v>0.1515356860150928</v>
+        <v>0.1729847975773228</v>
       </c>
       <c r="P35">
-        <v>0.198226311246089</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.22259616016291359</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>50</v>
       </c>
       <c r="B36">
-        <v>0.02269405592366902</v>
+        <v>2.3569670892876319E-2</v>
       </c>
       <c r="C36">
-        <v>0.03954187307517998</v>
+        <v>4.0617859195130952E-2</v>
       </c>
       <c r="D36">
-        <v>0.05546035068643396</v>
+        <v>5.8363748581773511E-2</v>
       </c>
       <c r="E36">
-        <v>0.05402509258612065</v>
+        <v>5.6789713485339233E-2</v>
       </c>
       <c r="F36">
-        <v>0.08201247469523998</v>
+        <v>8.4763615567789552E-2</v>
       </c>
       <c r="G36">
-        <v>0.07607262502043877</v>
+        <v>7.972557232247679E-2</v>
       </c>
       <c r="H36">
-        <v>0.08417325005779763</v>
+        <v>8.6659054018967785E-2</v>
       </c>
       <c r="I36">
-        <v>0.1393911057300362</v>
+        <v>0.1481920064811362</v>
       </c>
       <c r="J36">
-        <v>0.1167192238976292</v>
+        <v>0.1223606501747828</v>
       </c>
       <c r="K36">
-        <v>0.1143175313127633</v>
+        <v>0.11620450161006141</v>
       </c>
       <c r="L36">
-        <v>0.1257439587955957</v>
+        <v>0.1129302358466487</v>
       </c>
       <c r="M36">
-        <v>0.1460734416593187</v>
+        <v>0.12976951761295849</v>
       </c>
       <c r="N36">
-        <v>0.1645019692558283</v>
+        <v>0.14249708688415841</v>
       </c>
       <c r="O36">
-        <v>0.1867349282906661</v>
+        <v>0.15589231326144201</v>
       </c>
       <c r="P36">
-        <v>0.2290588952336958</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.21342354283829701</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>51</v>
       </c>
       <c r="B37">
-        <v>0.02586513495355236</v>
+        <v>2.2900004713740981E-2</v>
       </c>
       <c r="C37">
-        <v>0.04200255854440826</v>
+        <v>0.10731036417627191</v>
       </c>
       <c r="D37">
-        <v>0.05874446842779679</v>
+        <v>6.2934432571844501E-2</v>
       </c>
       <c r="E37">
-        <v>0.05659869460239975</v>
+        <v>7.899781379586035E-2</v>
       </c>
       <c r="F37">
-        <v>0.0847148020741193</v>
+        <v>0.1227247901054996</v>
       </c>
       <c r="G37">
-        <v>0.0812146488415918</v>
+        <v>0.206835030221213</v>
       </c>
       <c r="H37">
-        <v>0.08777100489319756</v>
+        <v>0.22514235586413589</v>
       </c>
       <c r="I37">
-        <v>0.1396929419191885</v>
+        <v>0.25066422510182379</v>
       </c>
       <c r="J37">
-        <v>0.1178870784797477</v>
+        <v>0.28502194028706118</v>
       </c>
       <c r="K37">
-        <v>0.1193941758672198</v>
+        <v>0.29817934621902048</v>
       </c>
       <c r="L37">
-        <v>0.1255718806762092</v>
+        <v>0.3263058731240317</v>
       </c>
       <c r="M37">
-        <v>0.1443050505258989</v>
+        <v>0.33578164951255379</v>
       </c>
       <c r="N37">
-        <v>0.1601903584262419</v>
+        <v>0.36103314932729041</v>
       </c>
       <c r="O37">
-        <v>0.1808726547060019</v>
+        <v>0.38224240571937268</v>
       </c>
       <c r="P37">
-        <v>0.2278450974276954</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>0.39553829920160283</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>52</v>
       </c>
       <c r="B38">
-        <v>0.02283838687121365</v>
+        <v>2.243946949818176E-2</v>
       </c>
       <c r="C38">
-        <v>0.03987504618512272</v>
+        <v>9.5310134488644449E-2</v>
       </c>
       <c r="D38">
-        <v>0.05628227093370031</v>
+        <v>5.534019262593548E-2</v>
       </c>
       <c r="E38">
-        <v>0.05430535271219572</v>
+        <v>6.6951017095788767E-2</v>
       </c>
       <c r="F38">
-        <v>0.08087313078575653</v>
+        <v>0.12209965841288201</v>
       </c>
       <c r="G38">
-        <v>0.07520041752475726</v>
+        <v>0.17368435341344499</v>
       </c>
       <c r="H38">
-        <v>0.08390903095946745</v>
+        <v>0.1775800485053497</v>
       </c>
       <c r="I38">
-        <v>0.133792500107715</v>
+        <v>0.19884752353062549</v>
       </c>
       <c r="J38">
-        <v>0.1135590392378466</v>
+        <v>0.20463019410006619</v>
       </c>
       <c r="K38">
-        <v>0.1115075986448053</v>
+        <v>0.1999246227102898</v>
       </c>
       <c r="L38">
-        <v>0.1190375939187585</v>
+        <v>0.20990900458997649</v>
       </c>
       <c r="M38">
-        <v>0.1347872946386013</v>
+        <v>0.22632352021750851</v>
       </c>
       <c r="N38">
-        <v>0.1520063659948238</v>
+        <v>0.23767547466449929</v>
       </c>
       <c r="O38">
-        <v>0.1729492117798199</v>
+        <v>0.26294784844190439</v>
       </c>
       <c r="P38">
-        <v>0.223343745192453</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.30524955512175889</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>53</v>
       </c>
       <c r="B39">
-        <v>0.0240907110771128</v>
+        <v>2.5361739929445348E-2</v>
       </c>
       <c r="C39">
-        <v>0.04157432442718034</v>
+        <v>0.102299779681277</v>
       </c>
       <c r="D39">
-        <v>0.05926490083750113</v>
+        <v>5.7555087159612987E-2</v>
       </c>
       <c r="E39">
-        <v>0.05586672336851883</v>
+        <v>6.929380872774904E-2</v>
       </c>
       <c r="F39">
-        <v>0.08350478001818773</v>
+        <v>0.1206840090192441</v>
       </c>
       <c r="G39">
-        <v>0.07999150382372255</v>
+        <v>0.17334766656067699</v>
       </c>
       <c r="H39">
-        <v>0.08513219859362808</v>
+        <v>0.15898180454025321</v>
       </c>
       <c r="I39">
-        <v>0.1404844171329034</v>
+        <v>0.17911312257145109</v>
       </c>
       <c r="J39">
-        <v>0.1179247301224806</v>
+        <v>0.19644037802651529</v>
       </c>
       <c r="K39">
-        <v>0.1140904594193056</v>
+        <v>0.20313793414434431</v>
       </c>
       <c r="L39">
-        <v>0.1202676263230389</v>
+        <v>0.21169582086526989</v>
       </c>
       <c r="M39">
-        <v>0.1374063750366044</v>
+        <v>0.23176266923812189</v>
       </c>
       <c r="N39">
-        <v>0.1525553776250811</v>
+        <v>0.23873115841166501</v>
       </c>
       <c r="O39">
-        <v>0.1684786812619019</v>
+        <v>0.25138162456362118</v>
       </c>
       <c r="P39">
-        <v>0.2178759259865662</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.29431215101203989</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>54</v>
       </c>
       <c r="B40">
-        <v>0.02383851925727065</v>
+        <v>2.710024209213369E-2</v>
       </c>
       <c r="C40">
-        <v>0.0399141565996346</v>
+        <v>6.5459470302231093E-2</v>
       </c>
       <c r="D40">
-        <v>0.05534342495934164</v>
+        <v>0.1123354543611262</v>
       </c>
       <c r="E40">
-        <v>0.05367208371963639</v>
+        <v>0.11536823438409199</v>
       </c>
       <c r="F40">
-        <v>0.07829985255725036</v>
+        <v>0.13523238184625941</v>
       </c>
       <c r="G40">
-        <v>0.07474058927905236</v>
+        <v>0.1424942174613629</v>
       </c>
       <c r="H40">
-        <v>0.08110836327598625</v>
+        <v>0.18489424308041219</v>
       </c>
       <c r="I40">
-        <v>0.1378261587221641</v>
+        <v>0.20337462211793361</v>
       </c>
       <c r="J40">
-        <v>0.1137008341368276</v>
+        <v>0.23292307703819709</v>
       </c>
       <c r="K40">
-        <v>0.1098738826616075</v>
+        <v>0.27887169614395629</v>
       </c>
       <c r="L40">
-        <v>0.1079289218407087</v>
+        <v>0.33126804248005659</v>
       </c>
       <c r="M40">
-        <v>0.1255700323879607</v>
+        <v>0.3804720786060245</v>
       </c>
       <c r="N40">
-        <v>0.1394446025024662</v>
+        <v>0.42422943882949848</v>
       </c>
       <c r="O40">
-        <v>0.1540482968266272</v>
+        <v>0.46786308397121712</v>
       </c>
       <c r="P40">
-        <v>0.2110362328103212</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.52881209010176611</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>55</v>
       </c>
       <c r="B41">
-        <v>0.02296230722617076</v>
+        <v>3.7441471748372757E-2</v>
       </c>
       <c r="C41">
-        <v>0.1067573612899597</v>
+        <v>5.7082535535852852E-2</v>
       </c>
       <c r="D41">
-        <v>0.06423337860387546</v>
+        <v>0.1227487377138287</v>
       </c>
       <c r="E41">
-        <v>0.08154846610385758</v>
+        <v>0.1894736150838594</v>
       </c>
       <c r="F41">
-        <v>0.1273207500670512</v>
+        <v>0.28865832237065869</v>
       </c>
       <c r="G41">
-        <v>0.2145222180851734</v>
+        <v>0.34878597103942899</v>
       </c>
       <c r="H41">
-        <v>0.2329509021981415</v>
+        <v>0.35055380690939519</v>
       </c>
       <c r="I41">
-        <v>0.26257096727896</v>
+        <v>0.35592085726700429</v>
       </c>
       <c r="J41">
-        <v>0.2933918292819877</v>
+        <v>0.38257944703496222</v>
       </c>
       <c r="K41">
-        <v>0.3074969287467262</v>
+        <v>0.46278431696454408</v>
       </c>
       <c r="L41">
-        <v>0.3437065639720925</v>
+        <v>0.54047145723154788</v>
       </c>
       <c r="M41">
-        <v>0.3534745323203832</v>
+        <v>0.58609557005735757</v>
       </c>
       <c r="N41">
-        <v>0.3770829749691709</v>
+        <v>0.6451123999253765</v>
       </c>
       <c r="O41">
-        <v>0.4006261147571942</v>
+        <v>0.68724204902047425</v>
       </c>
       <c r="P41">
-        <v>0.4163763698818056</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>0.6807972283535676</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>56</v>
       </c>
       <c r="B42">
-        <v>0.02266864139107894</v>
+        <v>4.5769542089812043E-2</v>
       </c>
       <c r="C42">
-        <v>0.09219698450705505</v>
+        <v>4.4622012031115599E-2</v>
       </c>
       <c r="D42">
-        <v>0.05038023849228435</v>
+        <v>0.1033655953582454</v>
       </c>
       <c r="E42">
-        <v>0.062781180025546</v>
+        <v>0.14756009272997669</v>
       </c>
       <c r="F42">
-        <v>0.1179948785156865</v>
+        <v>0.2298443208734933</v>
       </c>
       <c r="G42">
-        <v>0.1718202835346732</v>
+        <v>0.22707939563177379</v>
       </c>
       <c r="H42">
-        <v>0.17708874341111</v>
+        <v>0.26043128842088059</v>
       </c>
       <c r="I42">
-        <v>0.1940557118506935</v>
+        <v>0.33067724621253969</v>
       </c>
       <c r="J42">
-        <v>0.2067245147951428</v>
+        <v>0.41492874089086362</v>
       </c>
       <c r="K42">
-        <v>0.2033639168435611</v>
+        <v>0.51714379286561751</v>
       </c>
       <c r="L42">
-        <v>0.2110712310718336</v>
+        <v>0.55622925513156052</v>
       </c>
       <c r="M42">
-        <v>0.2295357892710376</v>
+        <v>0.59544901543834794</v>
       </c>
       <c r="N42">
-        <v>0.2437152637560631</v>
+        <v>0.62824471923257774</v>
       </c>
       <c r="O42">
-        <v>0.2704504996832486</v>
+        <v>0.64727007049447605</v>
       </c>
       <c r="P42">
-        <v>0.3116642027409174</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.64996018900324315</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>57</v>
       </c>
       <c r="B43">
-        <v>0.0213772561949116</v>
+        <v>2.9338446166903731E-2</v>
       </c>
       <c r="C43">
-        <v>0.09380639097853094</v>
+        <v>8.5571208703108637E-2</v>
       </c>
       <c r="D43">
-        <v>0.04958619688452204</v>
+        <v>0.12751977563449529</v>
       </c>
       <c r="E43">
-        <v>0.06242559509333379</v>
+        <v>0.1813134778996586</v>
       </c>
       <c r="F43">
-        <v>0.1107361437728017</v>
+        <v>0.32743218152778442</v>
       </c>
       <c r="G43">
-        <v>0.1621396590122685</v>
+        <v>0.32794958599369128</v>
       </c>
       <c r="H43">
-        <v>0.1508025801779133</v>
+        <v>0.32172522461051428</v>
       </c>
       <c r="I43">
-        <v>0.1678075119773956</v>
+        <v>0.32758857563452271</v>
       </c>
       <c r="J43">
-        <v>0.1851132491789066</v>
+        <v>0.41629591641889002</v>
       </c>
       <c r="K43">
-        <v>0.1908000328931494</v>
+        <v>0.43605548524178839</v>
       </c>
       <c r="L43">
-        <v>0.1986434248139197</v>
+        <v>0.49554858217206482</v>
       </c>
       <c r="M43">
-        <v>0.2181243947998454</v>
+        <v>0.51325201262409048</v>
       </c>
       <c r="N43">
-        <v>0.2264431074073245</v>
+        <v>0.52110279971224771</v>
       </c>
       <c r="O43">
-        <v>0.2413012315065765</v>
+        <v>0.52669078179090412</v>
       </c>
       <c r="P43">
-        <v>0.2787818924405309</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.02921323362104167</v>
-      </c>
-      <c r="C44">
-        <v>0.06830764600250283</v>
-      </c>
-      <c r="D44">
-        <v>0.1122246795910082</v>
-      </c>
-      <c r="E44">
-        <v>0.1165205769080613</v>
-      </c>
-      <c r="F44">
-        <v>0.1400247566575057</v>
-      </c>
-      <c r="G44">
-        <v>0.1484771944453249</v>
-      </c>
-      <c r="H44">
-        <v>0.1914547261059166</v>
-      </c>
-      <c r="I44">
-        <v>0.2100608193454444</v>
-      </c>
-      <c r="J44">
-        <v>0.2367634230273209</v>
-      </c>
-      <c r="K44">
-        <v>0.2827796068194708</v>
-      </c>
-      <c r="L44">
-        <v>0.3389489733182505</v>
-      </c>
-      <c r="M44">
-        <v>0.3869043364066737</v>
-      </c>
-      <c r="N44">
-        <v>0.4300711585997268</v>
-      </c>
-      <c r="O44">
-        <v>0.4719910436974463</v>
-      </c>
-      <c r="P44">
-        <v>0.5297998017902656</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.03851832418074497</v>
-      </c>
-      <c r="C45">
-        <v>0.05801083203324997</v>
-      </c>
-      <c r="D45">
-        <v>0.1242136196774658</v>
-      </c>
-      <c r="E45">
-        <v>0.189303544053843</v>
-      </c>
-      <c r="F45">
-        <v>0.2877276725704593</v>
-      </c>
-      <c r="G45">
-        <v>0.3521709945845252</v>
-      </c>
-      <c r="H45">
-        <v>0.3540853388379748</v>
-      </c>
-      <c r="I45">
-        <v>0.3600588963147838</v>
-      </c>
-      <c r="J45">
-        <v>0.3888633270969344</v>
-      </c>
-      <c r="K45">
-        <v>0.4731908751685333</v>
-      </c>
-      <c r="L45">
-        <v>0.5468955351254224</v>
-      </c>
-      <c r="M45">
-        <v>0.5912534279869761</v>
-      </c>
-      <c r="N45">
-        <v>0.6483473314708759</v>
-      </c>
-      <c r="O45">
-        <v>0.6824632588056516</v>
-      </c>
-      <c r="P45">
-        <v>0.6695172121415153</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.04539164192407907</v>
-      </c>
-      <c r="C46">
-        <v>0.04388461303693914</v>
-      </c>
-      <c r="D46">
-        <v>0.1052383734313415</v>
-      </c>
-      <c r="E46">
-        <v>0.1473683010691487</v>
-      </c>
-      <c r="F46">
-        <v>0.2335014676623282</v>
-      </c>
-      <c r="G46">
-        <v>0.2311053120957577</v>
-      </c>
-      <c r="H46">
-        <v>0.2632452185122121</v>
-      </c>
-      <c r="I46">
-        <v>0.3353679614193597</v>
-      </c>
-      <c r="J46">
-        <v>0.4231365195819494</v>
-      </c>
-      <c r="K46">
-        <v>0.5286549793233603</v>
-      </c>
-      <c r="L46">
-        <v>0.5661147281079628</v>
-      </c>
-      <c r="M46">
-        <v>0.6050164498728809</v>
-      </c>
-      <c r="N46">
-        <v>0.6374385336562063</v>
-      </c>
-      <c r="O46">
-        <v>0.6594148630668637</v>
-      </c>
-      <c r="P46">
-        <v>0.6667160558897303</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.02837450670379427</v>
-      </c>
-      <c r="C47">
-        <v>0.08475037849226463</v>
-      </c>
-      <c r="D47">
-        <v>0.1233626775810486</v>
-      </c>
-      <c r="E47">
-        <v>0.1755795164372449</v>
-      </c>
-      <c r="F47">
-        <v>0.31939105504906</v>
-      </c>
-      <c r="G47">
-        <v>0.3229437286065917</v>
-      </c>
-      <c r="H47">
-        <v>0.3162866577001512</v>
-      </c>
-      <c r="I47">
-        <v>0.3194349245293729</v>
-      </c>
-      <c r="J47">
-        <v>0.4029919273256174</v>
-      </c>
-      <c r="K47">
-        <v>0.4216376518932575</v>
-      </c>
-      <c r="L47">
-        <v>0.476911784014518</v>
-      </c>
-      <c r="M47">
-        <v>0.4983411161556993</v>
-      </c>
-      <c r="N47">
-        <v>0.5083925705225931</v>
-      </c>
-      <c r="O47">
-        <v>0.5155091581689806</v>
-      </c>
-      <c r="P47">
-        <v>0.520149718358228</v>
+        <v>0.53148820880074854</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:P43">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0.2</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>0.2</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>